--- a/xlsx/Power/p17.xlsx
+++ b/xlsx/Power/p17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A207C5-87B8-4307-B7E0-B1984C45277C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C0AC80-9C9E-408D-A941-D6478F995F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{2681C750-5823-4B15-9F10-6D011AC5A5BE}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{2681C750-5823-4B15-9F10-6D011AC5A5BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="C1">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="D1">
-        <v>0.106</v>
+        <v>2E-3</v>
       </c>
       <c r="E1">
-        <v>0.14899999999999999</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="F1">
-        <v>0.19</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G1">
-        <v>0.26</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="H1">
-        <v>0.32300000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="I1">
-        <v>0.35599999999999998</v>
+        <v>0.154</v>
       </c>
       <c r="J1">
-        <v>0.44400000000000001</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="C2">
-        <v>2.3E-2</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>3.7999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3.9E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="F2">
-        <v>6.9000000000000006E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="H2">
-        <v>0.13</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="I2">
-        <v>0.16200000000000001</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="J2">
-        <v>0.21299999999999999</v>
+        <v>8.1000000000000003E-2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,39 +468,39 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="C3">
-        <v>5.8000000000000003E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="D3">
-        <v>0.114</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="E3">
-        <v>0.122</v>
+        <v>0.129</v>
       </c>
       <c r="F3">
-        <v>0.153</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="G3">
         <v>0.19800000000000001</v>
       </c>
       <c r="H3">
-        <v>0.248</v>
+        <v>0.25</v>
       </c>
       <c r="I3">
-        <v>0.25700000000000001</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="J3">
-        <v>0.30099999999999999</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.04</v>
+        <v>5.5E-2</v>
       </c>
       <c r="B4">
-        <v>5.1999999999999998E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="C4">
-        <v>5.8000000000000003E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="D4">
         <v>9.6000000000000002E-2</v>
@@ -509,19 +509,19 @@
         <v>0.11</v>
       </c>
       <c r="F4">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="G4">
         <v>0.161</v>
       </c>
       <c r="H4">
-        <v>0.20499999999999999</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="I4">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="J4">
-        <v>0.215</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="F6">
-        <v>1E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G6">
-        <v>2E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="H6">
-        <v>1.4E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="I6">
-        <v>2.4E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="J6">
-        <v>4.2000000000000003E-2</v>
+        <v>6.4000000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="C7">
-        <v>7.1999999999999995E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="D7">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="E7">
-        <v>0.21</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F7">
-        <v>0.29299999999999998</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="G7">
-        <v>0.39400000000000002</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="H7">
-        <v>0.46899999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="I7">
-        <v>0.57399999999999995</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="J7">
-        <v>0.64100000000000001</v>
+        <v>0.63300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.124</v>
       </c>
       <c r="C8">
-        <v>0.13400000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.18</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E8">
-        <v>0.20899999999999999</v>
+        <v>4.7E-2</v>
       </c>
       <c r="F8">
-        <v>0.23300000000000001</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G8">
-        <v>0.27400000000000002</v>
+        <v>0.115</v>
       </c>
       <c r="H8">
-        <v>0.30499999999999999</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="I8">
-        <v>0.41199999999999998</v>
+        <v>3.9E-2</v>
       </c>
       <c r="J8">
-        <v>0.46800000000000003</v>
+        <v>4.1000000000000002E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="C9">
-        <v>2E-3</v>
+        <v>0.05</v>
       </c>
       <c r="D9">
-        <v>2.5000000000000001E-2</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="E9">
-        <v>0.08</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="F9">
-        <v>0.11799999999999999</v>
+        <v>0.248</v>
       </c>
       <c r="G9">
-        <v>0.14099999999999999</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="H9">
-        <v>0.20499999999999999</v>
+        <v>0.251</v>
       </c>
       <c r="I9">
-        <v>0.24299999999999999</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="J9">
-        <v>0.26900000000000002</v>
+        <v>0.29699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p17.xlsx
+++ b/xlsx/Power/p17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C0AC80-9C9E-408D-A941-D6478F995F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E00ED1-F85A-4DBB-AEBD-0FDF60A497CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{2681C750-5823-4B15-9F10-6D011AC5A5BE}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{2681C750-5823-4B15-9F10-6D011AC5A5BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="C1">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D1">
-        <v>2E-3</v>
+        <v>0.106</v>
       </c>
       <c r="E1">
-        <v>6.0000000000000001E-3</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="F1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.19</v>
       </c>
       <c r="G1">
-        <v>5.8000000000000003E-2</v>
+        <v>0.26</v>
       </c>
       <c r="H1">
-        <v>0.108</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="I1">
-        <v>0.154</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="J1">
-        <v>0.23400000000000001</v>
+        <v>0.44400000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2.3E-2</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="E2">
-        <v>1E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="F2">
-        <v>3.0000000000000001E-3</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G2">
-        <v>1.6E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
-        <v>3.5999999999999997E-2</v>
+        <v>0.13</v>
       </c>
       <c r="I2">
-        <v>5.2999999999999999E-2</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="J2">
-        <v>8.1000000000000003E-2</v>
+        <v>0.21299999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,39 +468,39 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="C3">
-        <v>8.3000000000000004E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="D3">
-        <v>0.11799999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="E3">
-        <v>0.129</v>
+        <v>0.122</v>
       </c>
       <c r="F3">
-        <v>0.16200000000000001</v>
+        <v>0.153</v>
       </c>
       <c r="G3">
         <v>0.19800000000000001</v>
       </c>
       <c r="H3">
-        <v>0.25</v>
+        <v>0.248</v>
       </c>
       <c r="I3">
-        <v>0.25800000000000001</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="J3">
-        <v>0.309</v>
+        <v>0.30099999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5.5E-2</v>
+        <v>0.04</v>
       </c>
       <c r="B4">
-        <v>5.7000000000000002E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="C4">
-        <v>6.2E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="D4">
         <v>9.6000000000000002E-2</v>
@@ -509,19 +509,19 @@
         <v>0.11</v>
       </c>
       <c r="F4">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="G4">
         <v>0.161</v>
       </c>
       <c r="H4">
-        <v>0.20200000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="I4">
-        <v>0.189</v>
+        <v>0.191</v>
       </c>
       <c r="J4">
-        <v>0.221</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>3.5999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>1E-3</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>2E-3</v>
       </c>
-      <c r="G6">
-        <v>6.0000000000000001E-3</v>
-      </c>
       <c r="H6">
-        <v>1.9E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I6">
-        <v>3.3000000000000002E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J6">
-        <v>6.4000000000000001E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="C7">
-        <v>6.9000000000000006E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="D7">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="E7">
-        <v>0.21299999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="F7">
-        <v>0.28699999999999998</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="G7">
-        <v>0.38500000000000001</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="H7">
-        <v>0.47</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="I7">
-        <v>0.56399999999999995</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="J7">
-        <v>0.63300000000000001</v>
+        <v>0.64100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.124</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="D8">
-        <v>6.0000000000000001E-3</v>
+        <v>0.18</v>
       </c>
       <c r="E8">
-        <v>4.7E-2</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="F8">
-        <v>7.6999999999999999E-2</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="G8">
-        <v>0.115</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="H8">
-        <v>0.16700000000000001</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I8">
-        <v>3.9E-2</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="J8">
-        <v>4.1000000000000002E-2</v>
+        <v>0.46800000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="C9">
-        <v>0.05</v>
+        <v>2E-3</v>
       </c>
       <c r="D9">
-        <v>0.72099999999999997</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E9">
-        <v>0.56899999999999995</v>
+        <v>0.08</v>
       </c>
       <c r="F9">
-        <v>0.248</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="G9">
-        <v>0.21199999999999999</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="H9">
-        <v>0.251</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="I9">
-        <v>0.26700000000000002</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="J9">
-        <v>0.29699999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p17.xlsx
+++ b/xlsx/Power/p17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E00ED1-F85A-4DBB-AEBD-0FDF60A497CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7752A011-71A1-4B26-9D11-473858745AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{2681C750-5823-4B15-9F10-6D011AC5A5BE}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{2681C750-5823-4B15-9F10-6D011AC5A5BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>3.7999999999999999E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="B1">
         <v>5.6000000000000001E-2</v>
@@ -407,25 +407,25 @@
         <v>0.06</v>
       </c>
       <c r="D1">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="E1">
-        <v>0.14899999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="F1">
         <v>0.19</v>
       </c>
       <c r="G1">
-        <v>0.26</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="H1">
         <v>0.32300000000000001</v>
       </c>
       <c r="I1">
-        <v>0.35599999999999998</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="J1">
-        <v>0.44400000000000001</v>
+        <v>0.45700000000000002</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -445,19 +445,19 @@
         <v>3.9E-2</v>
       </c>
       <c r="F2">
-        <v>6.9000000000000006E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H2">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="I2">
-        <v>0.16200000000000001</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="J2">
-        <v>0.21299999999999999</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,28 +468,28 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="C3">
-        <v>5.8000000000000003E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="D3">
         <v>0.114</v>
       </c>
       <c r="E3">
-        <v>0.122</v>
+        <v>0.128</v>
       </c>
       <c r="F3">
-        <v>0.153</v>
+        <v>0.155</v>
       </c>
       <c r="G3">
-        <v>0.19800000000000001</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="H3">
-        <v>0.248</v>
+        <v>0.251</v>
       </c>
       <c r="I3">
-        <v>0.25700000000000001</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="J3">
-        <v>0.30099999999999999</v>
+        <v>0.31900000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -500,65 +500,65 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="C4">
-        <v>5.8000000000000003E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="D4">
-        <v>9.6000000000000002E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E4">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="F4">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="G4">
-        <v>0.161</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="H4">
-        <v>0.20499999999999999</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="I4">
-        <v>0.191</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="J4">
-        <v>0.215</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1.2E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="B6">
         <v>6.0000000000000001E-3</v>
@@ -579,18 +579,18 @@
         <v>2E-3</v>
       </c>
       <c r="H6">
-        <v>1.4E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="I6">
-        <v>2.4E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="J6">
-        <v>4.2000000000000003E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1.0999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="B7">
         <v>2.8000000000000001E-2</v>
@@ -599,25 +599,25 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="D7">
-        <v>0.122</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="E7">
         <v>0.21</v>
       </c>
       <c r="F7">
-        <v>0.29199999999999998</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="G7">
-        <v>0.39400000000000002</v>
+        <v>0.39</v>
       </c>
       <c r="H7">
-        <v>0.46899999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="I7">
         <v>0.57399999999999995</v>
       </c>
       <c r="J7">
-        <v>0.64100000000000001</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -625,19 +625,19 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="B8">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="C8">
         <v>0.13400000000000001</v>
       </c>
       <c r="D8">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="E8">
-        <v>0.20899999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="F8">
-        <v>0.23300000000000001</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="G8">
         <v>0.27400000000000002</v>
@@ -646,10 +646,10 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="I8">
-        <v>0.41199999999999998</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="J8">
-        <v>0.46800000000000003</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -663,25 +663,25 @@
         <v>2E-3</v>
       </c>
       <c r="D9">
-        <v>2.5000000000000001E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="E9">
-        <v>0.08</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="F9">
         <v>0.11799999999999999</v>
       </c>
       <c r="G9">
-        <v>0.14099999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="H9">
         <v>0.20499999999999999</v>
       </c>
       <c r="I9">
-        <v>0.24299999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="J9">
-        <v>0.26900000000000002</v>
+        <v>0.27600000000000002</v>
       </c>
     </row>
   </sheetData>
